--- a/output/yearly_benthic_cover_iteration_37_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_37_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.16225353868771</v>
+        <v>45.0272199137915</v>
       </c>
       <c r="M2" t="n">
-        <v>99.49490411618632</v>
+        <v>100.4812397174091</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.06766323922621</v>
+        <v>88.11479694650708</v>
       </c>
       <c r="C3" t="n">
-        <v>45.96329765667045</v>
+        <v>45.95968025726492</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228807848291391</v>
+        <v>2.228931352495616</v>
       </c>
       <c r="E3" t="n">
-        <v>5.728258677691678</v>
+        <v>5.728870458270131</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429359494304636</v>
+        <v>0.7429771174985387</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98473025397829</v>
+        <v>33.98295952010719</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17505367380132</v>
+        <v>34.17694740493278</v>
       </c>
       <c r="I3" t="n">
-        <v>6.564527152092661</v>
+        <v>6.610504108836959</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643349683940397</v>
+        <v>4.643606984365867</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93233676077379</v>
+        <v>11.8852030534929</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86874088634428</v>
+        <v>48.91785486055695</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7643753037885</v>
+        <v>106.7627381713148</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.20362938834224</v>
+        <v>87.17803275170994</v>
       </c>
       <c r="C4" t="n">
-        <v>42.73243876074296</v>
+        <v>42.6650998242461</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187466784801321</v>
+        <v>2.18374692868914</v>
       </c>
       <c r="E4" t="n">
-        <v>6.535658396866295</v>
+        <v>6.532799532784109</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744492728011638</v>
+        <v>0.7445453706967016</v>
       </c>
       <c r="G4" t="n">
-        <v>33.35436416288631</v>
+        <v>33.29406416968035</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24666548853535</v>
+        <v>34.24908705204827</v>
       </c>
       <c r="I4" t="n">
-        <v>5.481902277168606</v>
+        <v>5.520381130956973</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653079550072738</v>
+        <v>4.653408566854385</v>
       </c>
       <c r="K4" t="n">
-        <v>12.79637061165775</v>
+        <v>12.82196724829008</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28884265115227</v>
+        <v>44.32930781332944</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81765202355298</v>
+        <v>99.81637488586561</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.07914504335852</v>
+        <v>86.0941652342503</v>
       </c>
       <c r="C5" t="n">
-        <v>42.45887304385526</v>
+        <v>42.43800808591249</v>
       </c>
       <c r="D5" t="n">
-        <v>2.132781552213887</v>
+        <v>2.131202506580216</v>
       </c>
       <c r="E5" t="n">
-        <v>7.134995815893657</v>
+        <v>7.143697649068036</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458120787255285</v>
+        <v>0.7458738605137818</v>
       </c>
       <c r="G5" t="n">
-        <v>32.52052697060221</v>
+        <v>32.49295606577407</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30735562137431</v>
+        <v>34.31019758363396</v>
       </c>
       <c r="I5" t="n">
-        <v>4.57634751251438</v>
+        <v>4.608525940469096</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661325492034552</v>
+        <v>4.661711628211137</v>
       </c>
       <c r="K5" t="n">
-        <v>13.92085495664146</v>
+        <v>13.9058347657497</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4679969362486</v>
+        <v>43.50281322803347</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84772493674532</v>
+        <v>99.84665607969565</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.74268547949771</v>
+        <v>84.75728577568893</v>
       </c>
       <c r="C6" t="n">
-        <v>41.83326067475699</v>
+        <v>41.81692367066211</v>
       </c>
       <c r="D6" t="n">
-        <v>2.067673320735691</v>
+        <v>2.066108890387779</v>
       </c>
       <c r="E6" t="n">
-        <v>7.553741801930752</v>
+        <v>7.566547947635327</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469325369029746</v>
+        <v>0.7470021078641655</v>
       </c>
       <c r="G6" t="n">
-        <v>31.52776050767168</v>
+        <v>31.50051916474157</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35889669753683</v>
+        <v>34.36209696175161</v>
       </c>
       <c r="I6" t="n">
-        <v>3.819352259076185</v>
+        <v>3.846247529157435</v>
       </c>
       <c r="J6" t="n">
-        <v>4.66832835564359</v>
+        <v>4.668763174151035</v>
       </c>
       <c r="K6" t="n">
-        <v>15.25731452050231</v>
+        <v>15.24271422431108</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78230404050417</v>
+        <v>42.81234749556934</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87287923576346</v>
+        <v>99.87198539054253</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.24637988735024</v>
+        <v>83.26508158717988</v>
       </c>
       <c r="C7" t="n">
-        <v>40.93026816663203</v>
+        <v>40.92217496783613</v>
       </c>
       <c r="D7" t="n">
-        <v>1.995029169706069</v>
+        <v>1.993714057513885</v>
       </c>
       <c r="E7" t="n">
-        <v>7.819496561412549</v>
+        <v>7.836309427624279</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478856777337924</v>
+        <v>0.7479618427035766</v>
       </c>
       <c r="G7" t="n">
-        <v>30.42008678911244</v>
+        <v>30.39676571254846</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40274117575445</v>
+        <v>34.40624476436452</v>
       </c>
       <c r="I7" t="n">
-        <v>3.186855027794756</v>
+        <v>3.209324265527817</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674285485836202</v>
+        <v>4.674761516897354</v>
       </c>
       <c r="K7" t="n">
-        <v>16.75362011264974</v>
+        <v>16.73491841282009</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21001860241057</v>
+        <v>42.23606641020051</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89390688169235</v>
+        <v>99.89315979085674</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.15421084365782</v>
+        <v>88.11950066286214</v>
       </c>
       <c r="C8" t="n">
-        <v>43.28749622783242</v>
+        <v>43.25398267277896</v>
       </c>
       <c r="D8" t="n">
-        <v>1.999264826147609</v>
+        <v>1.997944798794748</v>
       </c>
       <c r="E8" t="n">
-        <v>9.687960441323115</v>
+        <v>9.687305757398367</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494735175691845</v>
+        <v>0.7495490477656619</v>
       </c>
       <c r="G8" t="n">
-        <v>30.94270134325656</v>
+        <v>30.91096975676864</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47578180818248</v>
+        <v>34.47925619722045</v>
       </c>
       <c r="I8" t="n">
-        <v>5.614819422371481</v>
+        <v>5.60979355637887</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684209484807402</v>
+        <v>4.684681548535388</v>
       </c>
       <c r="K8" t="n">
-        <v>11.84578915634216</v>
+        <v>11.88049933713786</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67995048826945</v>
+        <v>44.6789208381857</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81323587244404</v>
+        <v>99.81340284810253</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.99672828285209</v>
+        <v>86.07392899146654</v>
       </c>
       <c r="C9" t="n">
-        <v>42.00175359837564</v>
+        <v>42.07933568327333</v>
       </c>
       <c r="D9" t="n">
-        <v>1.901531574567484</v>
+        <v>1.905448353640478</v>
       </c>
       <c r="E9" t="n">
-        <v>9.995621360912423</v>
+        <v>10.01937532248891</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508352633083035</v>
+        <v>0.7509084868872687</v>
       </c>
       <c r="G9" t="n">
-        <v>29.43007991592101</v>
+        <v>29.47992180164144</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53842211218196</v>
+        <v>34.54179039681436</v>
       </c>
       <c r="I9" t="n">
-        <v>4.687517660284001</v>
+        <v>4.683306586948641</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692720395676897</v>
+        <v>4.693178043045431</v>
       </c>
       <c r="K9" t="n">
-        <v>14.00327171714791</v>
+        <v>13.92607100853347</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83900747829946</v>
+        <v>43.8387657094049</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84403279382302</v>
+        <v>99.84417240121169</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.56934297276736</v>
+        <v>83.8815199954727</v>
       </c>
       <c r="C10" t="n">
-        <v>40.30172692410841</v>
+        <v>40.61370421685159</v>
       </c>
       <c r="D10" t="n">
-        <v>1.792636819124628</v>
+        <v>1.807356616887016</v>
       </c>
       <c r="E10" t="n">
-        <v>10.07526353347864</v>
+        <v>10.15505140804346</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752006960229333</v>
+        <v>0.7520748798208617</v>
       </c>
       <c r="G10" t="n">
-        <v>27.74471144874903</v>
+        <v>27.96230694561325</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59232017054931</v>
+        <v>34.59544447175964</v>
       </c>
       <c r="I10" t="n">
-        <v>3.912360539203095</v>
+        <v>3.908817674468083</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700043501433331</v>
+        <v>4.700467998880387</v>
       </c>
       <c r="K10" t="n">
-        <v>16.43065702723262</v>
+        <v>16.11848000452729</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1374072247622</v>
+        <v>43.13772392898366</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86979117610323</v>
+        <v>99.86990815036253</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.00000782088779</v>
+        <v>81.56251391916651</v>
       </c>
       <c r="C11" t="n">
-        <v>38.33866701792467</v>
+        <v>38.90067511773449</v>
       </c>
       <c r="D11" t="n">
-        <v>1.678615805226525</v>
+        <v>1.704646530609333</v>
       </c>
       <c r="E11" t="n">
-        <v>9.978537873138457</v>
+        <v>10.12156603824782</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530172739410785</v>
+        <v>0.7530773972285001</v>
       </c>
       <c r="G11" t="n">
-        <v>25.9800036752908</v>
+        <v>26.37323983396944</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63879460128961</v>
+        <v>34.64156027251101</v>
       </c>
       <c r="I11" t="n">
-        <v>3.264680629869574</v>
+        <v>3.261690113922272</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706357962131741</v>
+        <v>4.706733732678127</v>
       </c>
       <c r="K11" t="n">
-        <v>18.99999217911222</v>
+        <v>18.43748608083351</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55266412131856</v>
+        <v>42.55326053269676</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89132331835545</v>
+        <v>99.89142173126476</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.37509129500347</v>
+        <v>79.16519590744596</v>
       </c>
       <c r="C12" t="n">
-        <v>36.21868596697222</v>
+        <v>37.00822430415708</v>
       </c>
       <c r="D12" t="n">
-        <v>1.563353538297108</v>
+        <v>1.599497050111343</v>
       </c>
       <c r="E12" t="n">
-        <v>9.747314021763367</v>
+        <v>9.950758550190191</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538895779762895</v>
+        <v>0.7539402622060875</v>
       </c>
       <c r="G12" t="n">
-        <v>24.19608497922889</v>
+        <v>24.74643191936938</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67892058690931</v>
+        <v>34.68125206148002</v>
       </c>
       <c r="I12" t="n">
-        <v>2.723718728476697</v>
+        <v>2.721189425300875</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711809862351809</v>
+        <v>4.712126638788048</v>
       </c>
       <c r="K12" t="n">
-        <v>21.62490870499653</v>
+        <v>20.83480409255405</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06571975497933</v>
+        <v>42.06636910012436</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90931442694807</v>
+        <v>99.9093974968355</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.71051458408027</v>
+        <v>76.69826836512838</v>
       </c>
       <c r="C13" t="n">
-        <v>33.97435967418645</v>
+        <v>34.96164321529566</v>
       </c>
       <c r="D13" t="n">
-        <v>1.44747937599334</v>
+        <v>1.492256878693128</v>
       </c>
       <c r="E13" t="n">
-        <v>9.403525776597512</v>
+        <v>9.661913992695391</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546437067524503</v>
+        <v>0.7546840274387339</v>
       </c>
       <c r="G13" t="n">
-        <v>22.4026959540869</v>
+        <v>23.08727812422007</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71361051061271</v>
+        <v>34.71546526218176</v>
       </c>
       <c r="I13" t="n">
-        <v>2.272036092834552</v>
+        <v>2.269894908407215</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716523167202814</v>
+        <v>4.716775171492088</v>
       </c>
       <c r="K13" t="n">
-        <v>24.28948541591971</v>
+        <v>23.30173163487163</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66049605632504</v>
+        <v>41.66103655468547</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9243411464312</v>
+        <v>99.92441140485275</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.89194669607058</v>
+        <v>83.53769124853895</v>
       </c>
       <c r="C14" t="n">
-        <v>38.50664810436287</v>
+        <v>39.2157111395033</v>
       </c>
       <c r="D14" t="n">
-        <v>1.44913927953296</v>
+        <v>1.494001337582362</v>
       </c>
       <c r="E14" t="n">
-        <v>11.90368197234737</v>
+        <v>12.02960464128302</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555090978459369</v>
+        <v>0.7555662584265925</v>
       </c>
       <c r="G14" t="n">
-        <v>24.44247542800135</v>
+        <v>24.98238234704426</v>
       </c>
       <c r="H14" t="n">
-        <v>36.76750758163234</v>
+        <v>36.62416291835387</v>
       </c>
       <c r="I14" t="n">
-        <v>2.851701475173508</v>
+        <v>2.929684630682623</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721931861537105</v>
+        <v>4.722289115166205</v>
       </c>
       <c r="K14" t="n">
-        <v>17.10805330392943</v>
+        <v>16.46230875146109</v>
       </c>
       <c r="L14" t="n">
-        <v>44.29035075772785</v>
+        <v>44.22443798211865</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90505216602014</v>
+        <v>99.90245787308302</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.94019138418848</v>
+        <v>82.73656548691943</v>
       </c>
       <c r="C15" t="n">
-        <v>37.99034554884021</v>
+        <v>38.86732946586712</v>
       </c>
       <c r="D15" t="n">
-        <v>1.413464518853847</v>
+        <v>1.464358654200102</v>
       </c>
       <c r="E15" t="n">
-        <v>12.01187046078243</v>
+        <v>12.19822488917032</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562401768844595</v>
+        <v>0.756310169156848</v>
       </c>
       <c r="G15" t="n">
-        <v>23.84553228622145</v>
+        <v>24.48670350699291</v>
       </c>
       <c r="H15" t="n">
-        <v>36.80786536563296</v>
+        <v>36.66022210903071</v>
       </c>
       <c r="I15" t="n">
-        <v>2.378717470285464</v>
+        <v>2.443807601138249</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726501105527872</v>
+        <v>4.726938557230302</v>
       </c>
       <c r="K15" t="n">
-        <v>18.0598086158115</v>
+        <v>17.26343451308057</v>
       </c>
       <c r="L15" t="n">
-        <v>43.87063190548236</v>
+        <v>43.78785589242226</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92078607013408</v>
+        <v>99.91861987136994</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.22452997208619</v>
+        <v>80.27050361114483</v>
       </c>
       <c r="C16" t="n">
-        <v>35.64182345706841</v>
+        <v>36.77895306612589</v>
       </c>
       <c r="D16" t="n">
-        <v>1.311569358896151</v>
+        <v>1.370858294897514</v>
       </c>
       <c r="E16" t="n">
-        <v>11.47660064328261</v>
+        <v>11.75906441224894</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568714289345931</v>
+        <v>0.7569503105258328</v>
       </c>
       <c r="G16" t="n">
-        <v>22.12653312198974</v>
+        <v>22.92320977581377</v>
       </c>
       <c r="H16" t="n">
-        <v>36.83858978518023</v>
+        <v>36.69125134243944</v>
       </c>
       <c r="I16" t="n">
-        <v>1.983919202961657</v>
+        <v>2.038230034432868</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730446430841206</v>
+        <v>4.730939440786456</v>
       </c>
       <c r="K16" t="n">
-        <v>20.77547002791381</v>
+        <v>19.72949638885518</v>
       </c>
       <c r="L16" t="n">
-        <v>43.51663102973205</v>
+        <v>43.42366700054288</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93392451471428</v>
+        <v>99.93211645552395</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.98950617730407</v>
+        <v>81.99039796178367</v>
       </c>
       <c r="C17" t="n">
-        <v>36.93163648315902</v>
+        <v>38.03841035059431</v>
       </c>
       <c r="D17" t="n">
-        <v>1.312626421677744</v>
+        <v>1.371983037663939</v>
       </c>
       <c r="E17" t="n">
-        <v>12.27957324486548</v>
+        <v>12.55155586141229</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574814314575643</v>
+        <v>0.7575713625991768</v>
       </c>
       <c r="G17" t="n">
-        <v>22.6117205349194</v>
+        <v>23.38850931531916</v>
       </c>
       <c r="H17" t="n">
-        <v>37.33563441895291</v>
+        <v>37.16784709338954</v>
       </c>
       <c r="I17" t="n">
-        <v>1.958211178821198</v>
+        <v>2.018110275154718</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734258946609776</v>
+        <v>4.734821016244856</v>
       </c>
       <c r="K17" t="n">
-        <v>19.01049382269594</v>
+        <v>18.00960203821632</v>
       </c>
       <c r="L17" t="n">
-        <v>43.99264855333465</v>
+        <v>43.88477241647325</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93477885918961</v>
+        <v>99.93278480528389</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.3781358238239</v>
+        <v>79.64954818820871</v>
       </c>
       <c r="C18" t="n">
-        <v>34.62200505427629</v>
+        <v>36.00906289719109</v>
       </c>
       <c r="D18" t="n">
-        <v>1.218793192974745</v>
+        <v>1.286814478422775</v>
       </c>
       <c r="E18" t="n">
-        <v>11.6739294020011</v>
+        <v>12.05288372646582</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580074918358619</v>
+        <v>0.7581049289049745</v>
       </c>
       <c r="G18" t="n">
-        <v>20.99531947115786</v>
+        <v>21.93662136444772</v>
       </c>
       <c r="H18" t="n">
-        <v>37.36156350071089</v>
+        <v>37.19402483960216</v>
       </c>
       <c r="I18" t="n">
-        <v>1.632975941169279</v>
+        <v>1.682943044709177</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737546823974136</v>
+        <v>4.738155805656092</v>
       </c>
       <c r="K18" t="n">
-        <v>21.62186417617612</v>
+        <v>20.35045181179128</v>
       </c>
       <c r="L18" t="n">
-        <v>43.70173601458035</v>
+        <v>43.58442667226333</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94560524503275</v>
+        <v>99.94394138124571</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.31967435396723</v>
+        <v>78.7327332771208</v>
       </c>
       <c r="C19" t="n">
-        <v>33.80788922340822</v>
+        <v>35.3513516766963</v>
       </c>
       <c r="D19" t="n">
-        <v>1.181149934680071</v>
+        <v>1.254115421615769</v>
       </c>
       <c r="E19" t="n">
-        <v>11.54135728089104</v>
+        <v>11.98049059826461</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584545047035436</v>
+        <v>0.7585553293936819</v>
       </c>
       <c r="G19" t="n">
-        <v>20.34686472232308</v>
+        <v>21.37919304810716</v>
       </c>
       <c r="H19" t="n">
-        <v>37.38359639592816</v>
+        <v>37.21612231757127</v>
       </c>
       <c r="I19" t="n">
-        <v>1.367910861044199</v>
+        <v>1.403285753457788</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740340654397146</v>
+        <v>4.740970808710513</v>
       </c>
       <c r="K19" t="n">
-        <v>22.68032564603277</v>
+        <v>21.26726672287921</v>
       </c>
       <c r="L19" t="n">
-        <v>43.46621497553081</v>
+        <v>43.3346331825159</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9544298449718</v>
+        <v>99.95325158209141</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.49837688888796</v>
+        <v>76.20758000702756</v>
       </c>
       <c r="C20" t="n">
-        <v>31.19651659710793</v>
+        <v>33.04210192637935</v>
       </c>
       <c r="D20" t="n">
-        <v>1.080932023508066</v>
+        <v>1.163219911966241</v>
       </c>
       <c r="E20" t="n">
-        <v>10.75218368618509</v>
+        <v>11.30717170153365</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758841548033552</v>
+        <v>0.7589435288358415</v>
       </c>
       <c r="G20" t="n">
-        <v>18.62047908617359</v>
+        <v>19.82967646094992</v>
       </c>
       <c r="H20" t="n">
-        <v>37.40267344214126</v>
+        <v>37.23516809757333</v>
       </c>
       <c r="I20" t="n">
-        <v>1.140507427636702</v>
+        <v>1.170003250944561</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742759675209698</v>
+        <v>4.74339705522401</v>
       </c>
       <c r="K20" t="n">
-        <v>25.50162311111204</v>
+        <v>23.79241999297243</v>
       </c>
       <c r="L20" t="n">
-        <v>43.26386276786214</v>
+        <v>43.12649792082994</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96200247608211</v>
+        <v>99.96101984018173</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.89326544985674</v>
+        <v>82.04009403057266</v>
       </c>
       <c r="C21" t="n">
-        <v>35.25140275780921</v>
+        <v>36.67743714314123</v>
       </c>
       <c r="D21" t="n">
-        <v>1.081624945256757</v>
+        <v>1.164003938250423</v>
       </c>
       <c r="E21" t="n">
-        <v>12.90949380537766</v>
+        <v>13.26346548650494</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593279965807385</v>
+        <v>0.7594550672549277</v>
       </c>
       <c r="G21" t="n">
-        <v>20.5235536051805</v>
+        <v>21.51523375026347</v>
       </c>
       <c r="H21" t="n">
-        <v>39.31778811785956</v>
+        <v>38.93245692861156</v>
       </c>
       <c r="I21" t="n">
-        <v>1.555677000971891</v>
+        <v>1.658884689344039</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745799978629614</v>
+        <v>4.746594170343299</v>
       </c>
       <c r="K21" t="n">
-        <v>19.10673455014325</v>
+        <v>17.95990596942735</v>
       </c>
       <c r="L21" t="n">
-        <v>45.59004001247764</v>
+        <v>45.30739797638909</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9481773204301</v>
+        <v>99.94474108895767</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_37_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_37_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.0272199137915</v>
+        <v>45.45149506921209</v>
       </c>
       <c r="M2" t="n">
-        <v>100.4812397174091</v>
+        <v>99.48498799293822</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.11479694650708</v>
+        <v>87.95058982549477</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95968025726492</v>
+        <v>45.87757144713562</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228931352495616</v>
+        <v>2.228572451674404</v>
       </c>
       <c r="E3" t="n">
-        <v>5.728870458270131</v>
+        <v>5.673020101311374</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429771174985387</v>
+        <v>0.7428574838914682</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98295952010719</v>
+        <v>33.95617157846053</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17694740493278</v>
+        <v>34.17144425900754</v>
       </c>
       <c r="I3" t="n">
-        <v>6.610504108836959</v>
+        <v>6.535664676827774</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643606984365867</v>
+        <v>4.642859274321676</v>
       </c>
       <c r="K3" t="n">
-        <v>11.8852030534929</v>
+        <v>12.04941017450522</v>
       </c>
       <c r="L3" t="n">
-        <v>48.91785486055695</v>
+        <v>48.83840488228306</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7627381713148</v>
+        <v>106.7653865039239</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.17803275170994</v>
+        <v>87.03890193383434</v>
       </c>
       <c r="C4" t="n">
-        <v>42.6650998242461</v>
+        <v>42.59666492879234</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18374692868914</v>
+        <v>2.184589399740646</v>
       </c>
       <c r="E4" t="n">
-        <v>6.532799532784109</v>
+        <v>6.470686027470659</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445453706967016</v>
+        <v>0.74441017891356</v>
       </c>
       <c r="G4" t="n">
-        <v>33.29406416968035</v>
+        <v>33.28601339855263</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24908705204827</v>
+        <v>34.24286823002376</v>
       </c>
       <c r="I4" t="n">
-        <v>5.520381130956973</v>
+        <v>5.45777108092334</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653408566854385</v>
+        <v>4.65256361820975</v>
       </c>
       <c r="K4" t="n">
-        <v>12.82196724829008</v>
+        <v>12.96109806616564</v>
       </c>
       <c r="L4" t="n">
-        <v>44.32930781332944</v>
+        <v>44.26069076401903</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81637488586561</v>
+        <v>99.818453758977</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.0941652342503</v>
+        <v>85.85418334386563</v>
       </c>
       <c r="C5" t="n">
-        <v>42.43800808591249</v>
+        <v>42.25900417594814</v>
       </c>
       <c r="D5" t="n">
-        <v>2.131202506580216</v>
+        <v>2.126636446201062</v>
       </c>
       <c r="E5" t="n">
-        <v>7.143697649068036</v>
+        <v>7.058395854787079</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458738605137818</v>
+        <v>0.7457270135129337</v>
       </c>
       <c r="G5" t="n">
-        <v>32.49295606577407</v>
+        <v>32.402999506682</v>
       </c>
       <c r="H5" t="n">
-        <v>34.31019758363396</v>
+        <v>34.30344262159495</v>
       </c>
       <c r="I5" t="n">
-        <v>4.608525940469096</v>
+        <v>4.556188066631769</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661711628211137</v>
+        <v>4.660793834455835</v>
       </c>
       <c r="K5" t="n">
-        <v>13.9058347657497</v>
+        <v>14.14581665613435</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50281322803347</v>
+        <v>43.44357441566962</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84665607969565</v>
+        <v>99.84839524775212</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.75728577568893</v>
+        <v>84.47266998043949</v>
       </c>
       <c r="C6" t="n">
-        <v>41.81692367066211</v>
+        <v>41.58504935590025</v>
       </c>
       <c r="D6" t="n">
-        <v>2.066108890387779</v>
+        <v>2.059076684684114</v>
       </c>
       <c r="E6" t="n">
-        <v>7.566547947635327</v>
+        <v>7.467915579578186</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7470021078641655</v>
+        <v>0.7468459719701123</v>
       </c>
       <c r="G6" t="n">
-        <v>31.50051916474157</v>
+        <v>31.37360921149741</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36209696175161</v>
+        <v>34.35491471062516</v>
       </c>
       <c r="I6" t="n">
-        <v>3.846247529157435</v>
+        <v>3.802520497271322</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668763174151035</v>
+        <v>4.667787324813201</v>
       </c>
       <c r="K6" t="n">
-        <v>15.24271422431108</v>
+        <v>15.52733001956049</v>
       </c>
       <c r="L6" t="n">
-        <v>42.81234749556934</v>
+        <v>42.76105984491059</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87198539054253</v>
+        <v>99.87343922037132</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.26508158717988</v>
+        <v>82.87667465251677</v>
       </c>
       <c r="C7" t="n">
-        <v>40.92217496783613</v>
+        <v>40.57957996665031</v>
       </c>
       <c r="D7" t="n">
-        <v>1.993714057513885</v>
+        <v>1.981253891129603</v>
       </c>
       <c r="E7" t="n">
-        <v>7.836309427624279</v>
+        <v>7.71446754552068</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479618427035766</v>
+        <v>0.7477990350506681</v>
       </c>
       <c r="G7" t="n">
-        <v>30.39676571254846</v>
+        <v>30.18784379980229</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40624476436452</v>
+        <v>34.39875561233073</v>
       </c>
       <c r="I7" t="n">
-        <v>3.209324265527817</v>
+        <v>3.172810799616117</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674761516897354</v>
+        <v>4.673743969066675</v>
       </c>
       <c r="K7" t="n">
-        <v>16.73491841282009</v>
+        <v>17.12332534748323</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23606641020051</v>
+        <v>42.1914691164978</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89315979085674</v>
+        <v>99.89437443063134</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.11950066286214</v>
+        <v>87.83220540927729</v>
       </c>
       <c r="C8" t="n">
-        <v>43.25398267277896</v>
+        <v>42.90518810186798</v>
       </c>
       <c r="D8" t="n">
-        <v>1.997944798794748</v>
+        <v>1.985523131373752</v>
       </c>
       <c r="E8" t="n">
-        <v>9.687305757398367</v>
+        <v>9.565677083283553</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495490477656619</v>
+        <v>0.7494104053799669</v>
       </c>
       <c r="G8" t="n">
-        <v>30.91096975676864</v>
+        <v>30.6970303252282</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47925619722045</v>
+        <v>34.47287864747848</v>
       </c>
       <c r="I8" t="n">
-        <v>5.60979355637887</v>
+        <v>5.677870782908548</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684681548535388</v>
+        <v>4.683815033624793</v>
       </c>
       <c r="K8" t="n">
-        <v>11.88049933713786</v>
+        <v>12.16779459072271</v>
       </c>
       <c r="L8" t="n">
-        <v>44.6789208381857</v>
+        <v>44.73816189689279</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81340284810253</v>
+        <v>99.81114458948348</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.07392899146654</v>
+        <v>85.83711336746617</v>
       </c>
       <c r="C9" t="n">
-        <v>42.07933568327333</v>
+        <v>41.79114206774723</v>
       </c>
       <c r="D9" t="n">
-        <v>1.905448353640478</v>
+        <v>1.895242944519623</v>
       </c>
       <c r="E9" t="n">
-        <v>10.01937532248891</v>
+        <v>9.920778020036678</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7509084868872687</v>
+        <v>0.7507899200807023</v>
       </c>
       <c r="G9" t="n">
-        <v>29.47992180164144</v>
+        <v>29.30126031890699</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54179039681436</v>
+        <v>34.53633632371231</v>
       </c>
       <c r="I9" t="n">
-        <v>4.683306586948641</v>
+        <v>4.740268839705494</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693178043045431</v>
+        <v>4.692437000504389</v>
       </c>
       <c r="K9" t="n">
-        <v>13.92607100853347</v>
+        <v>14.16288663253381</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8387657094049</v>
+        <v>43.8882526668604</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84417240121169</v>
+        <v>99.84228136714144</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.8815199954727</v>
+        <v>83.62661828824652</v>
       </c>
       <c r="C10" t="n">
-        <v>40.61370421685159</v>
+        <v>40.31594679650564</v>
       </c>
       <c r="D10" t="n">
-        <v>1.807356616887016</v>
+        <v>1.796181473448327</v>
       </c>
       <c r="E10" t="n">
-        <v>10.15505140804346</v>
+        <v>10.06164295941691</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520748798208617</v>
+        <v>0.7519739392314666</v>
       </c>
       <c r="G10" t="n">
-        <v>27.96230694561325</v>
+        <v>27.76972793155406</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59544447175964</v>
+        <v>34.59080120464747</v>
       </c>
       <c r="I10" t="n">
-        <v>3.908817674468083</v>
+        <v>3.95645365975163</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700467998880387</v>
+        <v>4.699837120196666</v>
       </c>
       <c r="K10" t="n">
-        <v>16.11848000452729</v>
+        <v>16.37338171175347</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13772392898366</v>
+        <v>43.17899735730462</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86990815036253</v>
+        <v>99.86832586556372</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.56251391916651</v>
+        <v>81.31804790714712</v>
       </c>
       <c r="C11" t="n">
-        <v>38.90067511773449</v>
+        <v>38.62046337529465</v>
       </c>
       <c r="D11" t="n">
-        <v>1.704646530609333</v>
+        <v>1.693831086225341</v>
       </c>
       <c r="E11" t="n">
-        <v>10.12156603824782</v>
+        <v>10.03855944059215</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530773972285001</v>
+        <v>0.7529916087686005</v>
       </c>
       <c r="G11" t="n">
-        <v>26.37323983396944</v>
+        <v>26.18734750458364</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64156027251101</v>
+        <v>34.63761400335563</v>
       </c>
       <c r="I11" t="n">
-        <v>3.261690113922272</v>
+        <v>3.301506708818015</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706733732678127</v>
+        <v>4.706197554803753</v>
       </c>
       <c r="K11" t="n">
-        <v>18.43748608083351</v>
+        <v>18.68195209285287</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55326053269676</v>
+        <v>42.58768304130383</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89142173126476</v>
+        <v>99.89009850945135</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.16519590744596</v>
+        <v>78.88218316932488</v>
       </c>
       <c r="C12" t="n">
-        <v>37.00822430415708</v>
+        <v>36.69540750079442</v>
       </c>
       <c r="D12" t="n">
-        <v>1.599497050111343</v>
+        <v>1.586868705322758</v>
       </c>
       <c r="E12" t="n">
-        <v>9.950758550190191</v>
+        <v>9.863718821985378</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539402622060875</v>
+        <v>0.7538680566651994</v>
       </c>
       <c r="G12" t="n">
-        <v>24.74643191936938</v>
+        <v>24.5336636978614</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68125206148002</v>
+        <v>34.67793060659918</v>
       </c>
       <c r="I12" t="n">
-        <v>2.721189425300875</v>
+        <v>2.754457926733474</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712126638788048</v>
+        <v>4.711675354157496</v>
       </c>
       <c r="K12" t="n">
-        <v>20.83480409255405</v>
+        <v>21.11781683067512</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06636910012436</v>
+        <v>42.09506714884106</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9093974968355</v>
+        <v>99.90829148031061</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.69826836512838</v>
+        <v>76.40497386083445</v>
       </c>
       <c r="C13" t="n">
-        <v>34.96164321529566</v>
+        <v>34.64347357427948</v>
       </c>
       <c r="D13" t="n">
-        <v>1.492256878693128</v>
+        <v>1.47910749971269</v>
       </c>
       <c r="E13" t="n">
-        <v>9.661913992695391</v>
+        <v>9.576839711760776</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546840274387339</v>
+        <v>0.7546237445805013</v>
       </c>
       <c r="G13" t="n">
-        <v>23.08727812422007</v>
+        <v>22.86762972211684</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71546526218176</v>
+        <v>34.71269225070306</v>
       </c>
       <c r="I13" t="n">
-        <v>2.269894908407215</v>
+        <v>2.297682528332427</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716775171492088</v>
+        <v>4.716398403628133</v>
       </c>
       <c r="K13" t="n">
-        <v>23.30173163487163</v>
+        <v>23.59502613916558</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66103655468547</v>
+        <v>41.68498756636789</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92441140485275</v>
+        <v>99.92348727981295</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.53769124853895</v>
+        <v>83.30200307718037</v>
       </c>
       <c r="C14" t="n">
-        <v>39.2157111395033</v>
+        <v>39.01749067001647</v>
       </c>
       <c r="D14" t="n">
-        <v>1.494001337582362</v>
+        <v>1.480782677600891</v>
       </c>
       <c r="E14" t="n">
-        <v>12.02960464128302</v>
+        <v>11.99564958279398</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555662584265925</v>
+        <v>0.7554784011967905</v>
       </c>
       <c r="G14" t="n">
-        <v>24.98238234704426</v>
+        <v>24.82976965497598</v>
       </c>
       <c r="H14" t="n">
-        <v>36.62416291835387</v>
+        <v>36.68824742676535</v>
       </c>
       <c r="I14" t="n">
-        <v>2.929684630682623</v>
+        <v>2.830335326367454</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722289115166205</v>
+        <v>4.72174000747994</v>
       </c>
       <c r="K14" t="n">
-        <v>16.46230875146109</v>
+        <v>16.69799692281962</v>
       </c>
       <c r="L14" t="n">
-        <v>44.22443798211865</v>
+        <v>44.19027462621972</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90245787308302</v>
+        <v>99.90576221905582</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.73656548691943</v>
+        <v>82.5170565177269</v>
       </c>
       <c r="C15" t="n">
-        <v>38.86732946586712</v>
+        <v>38.66983588577629</v>
       </c>
       <c r="D15" t="n">
-        <v>1.464358654200102</v>
+        <v>1.451822676283683</v>
       </c>
       <c r="E15" t="n">
-        <v>12.19822488917032</v>
+        <v>12.15452497909294</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756310169156848</v>
+        <v>0.75619889076876</v>
       </c>
       <c r="G15" t="n">
-        <v>24.48670350699291</v>
+        <v>24.34416824108108</v>
       </c>
       <c r="H15" t="n">
-        <v>36.66022210903071</v>
+        <v>36.72323651400193</v>
       </c>
       <c r="I15" t="n">
-        <v>2.443807601138249</v>
+        <v>2.36086214919376</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726938557230302</v>
+        <v>4.72624306730475</v>
       </c>
       <c r="K15" t="n">
-        <v>17.26343451308057</v>
+        <v>17.48294348227311</v>
       </c>
       <c r="L15" t="n">
-        <v>43.78785589242226</v>
+        <v>43.76860020621817</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91861987136994</v>
+        <v>99.92137957426756</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.27050361114483</v>
+        <v>80.03255742006652</v>
       </c>
       <c r="C16" t="n">
-        <v>36.77895306612589</v>
+        <v>36.55011321028746</v>
       </c>
       <c r="D16" t="n">
-        <v>1.370858294897514</v>
+        <v>1.35788914981084</v>
       </c>
       <c r="E16" t="n">
-        <v>11.75906441224894</v>
+        <v>11.69628861919508</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569503105258328</v>
+        <v>0.7568190361035405</v>
       </c>
       <c r="G16" t="n">
-        <v>22.92320977581377</v>
+        <v>22.76909050652852</v>
       </c>
       <c r="H16" t="n">
-        <v>36.69125134243944</v>
+        <v>36.75335259071165</v>
       </c>
       <c r="I16" t="n">
-        <v>2.038230034432868</v>
+        <v>1.968998542069765</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730939440786456</v>
+        <v>4.730118975647128</v>
       </c>
       <c r="K16" t="n">
-        <v>19.72949638885518</v>
+        <v>19.96744257993348</v>
       </c>
       <c r="L16" t="n">
-        <v>43.42366700054288</v>
+        <v>43.41686470563481</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93211645552395</v>
+        <v>99.93442049585573</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.99039796178367</v>
+        <v>81.84386229944781</v>
       </c>
       <c r="C17" t="n">
-        <v>38.03841035059431</v>
+        <v>37.87498873240698</v>
       </c>
       <c r="D17" t="n">
-        <v>1.371983037663939</v>
+        <v>1.358959953059777</v>
       </c>
       <c r="E17" t="n">
-        <v>12.55155586141229</v>
+        <v>12.5148242818011</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575713625991768</v>
+        <v>0.7574158479145999</v>
       </c>
       <c r="G17" t="n">
-        <v>23.38850931531916</v>
+        <v>23.27365608100005</v>
       </c>
       <c r="H17" t="n">
-        <v>37.16784709338954</v>
+        <v>37.2689458645177</v>
       </c>
       <c r="I17" t="n">
-        <v>2.018110275154718</v>
+        <v>1.936211221688321</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734821016244856</v>
+        <v>4.733849049466249</v>
       </c>
       <c r="K17" t="n">
-        <v>18.00960203821632</v>
+        <v>18.1561377005522</v>
       </c>
       <c r="L17" t="n">
-        <v>43.88477241647325</v>
+        <v>43.90438404808303</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93278480528389</v>
+        <v>99.9355104810422</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.64954818820871</v>
+        <v>79.46828810957362</v>
       </c>
       <c r="C18" t="n">
-        <v>36.00906289719109</v>
+        <v>35.79820019913585</v>
       </c>
       <c r="D18" t="n">
-        <v>1.286814478422775</v>
+        <v>1.272916134766849</v>
       </c>
       <c r="E18" t="n">
-        <v>12.05288372646582</v>
+        <v>11.99153684795485</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581049289049745</v>
+        <v>0.75792880943708</v>
       </c>
       <c r="G18" t="n">
-        <v>21.93662136444772</v>
+        <v>21.80006281554965</v>
       </c>
       <c r="H18" t="n">
-        <v>37.19402483960216</v>
+        <v>37.2941863387757</v>
       </c>
       <c r="I18" t="n">
-        <v>1.682943044709177</v>
+        <v>1.614602104107729</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738155805656092</v>
+        <v>4.737055058981749</v>
       </c>
       <c r="K18" t="n">
-        <v>20.35045181179128</v>
+        <v>20.53171189042637</v>
       </c>
       <c r="L18" t="n">
-        <v>43.58442667226333</v>
+        <v>43.61630426539089</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94394138124571</v>
+        <v>99.94621635495312</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.7327332771208</v>
+        <v>78.56865378331003</v>
       </c>
       <c r="C19" t="n">
-        <v>35.3513516766963</v>
+        <v>35.147060573682</v>
       </c>
       <c r="D19" t="n">
-        <v>1.254115421615769</v>
+        <v>1.240965896555288</v>
       </c>
       <c r="E19" t="n">
-        <v>11.98049059826461</v>
+        <v>11.91492724201635</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585553293936819</v>
+        <v>0.7583617119429414</v>
       </c>
       <c r="G19" t="n">
-        <v>21.37919304810716</v>
+        <v>21.25288049853757</v>
       </c>
       <c r="H19" t="n">
-        <v>37.21612231757127</v>
+        <v>37.31548747750944</v>
       </c>
       <c r="I19" t="n">
-        <v>1.403285753457788</v>
+        <v>1.346270257105044</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740970808710513</v>
+        <v>4.739760699643383</v>
       </c>
       <c r="K19" t="n">
-        <v>21.26726672287921</v>
+        <v>21.43134621668998</v>
       </c>
       <c r="L19" t="n">
-        <v>43.3346331825159</v>
+        <v>43.37674315118056</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95325158209141</v>
+        <v>99.95514994155255</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.20758000702756</v>
+        <v>75.93971996340088</v>
       </c>
       <c r="C20" t="n">
-        <v>33.04210192637935</v>
+        <v>32.72518350929648</v>
       </c>
       <c r="D20" t="n">
-        <v>1.163219911966241</v>
+        <v>1.146717067806402</v>
       </c>
       <c r="E20" t="n">
-        <v>11.30717170153365</v>
+        <v>11.19708692437004</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589435288358415</v>
+        <v>0.7587353499764223</v>
       </c>
       <c r="G20" t="n">
-        <v>19.82967646094992</v>
+        <v>19.63876757239885</v>
       </c>
       <c r="H20" t="n">
-        <v>37.23516809757333</v>
+        <v>37.33387248447895</v>
       </c>
       <c r="I20" t="n">
-        <v>1.170003250944561</v>
+        <v>1.122444627017573</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74339705522401</v>
+        <v>4.742095937352638</v>
       </c>
       <c r="K20" t="n">
-        <v>23.79241999297243</v>
+        <v>24.06028003659913</v>
       </c>
       <c r="L20" t="n">
-        <v>43.12649792082994</v>
+        <v>43.1771400580737</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96101984018173</v>
+        <v>99.96260360396931</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.04009403057266</v>
+        <v>81.92589713761465</v>
       </c>
       <c r="C21" t="n">
-        <v>36.67743714314123</v>
+        <v>36.49734719126532</v>
       </c>
       <c r="D21" t="n">
-        <v>1.164003938250423</v>
+        <v>1.147441716354094</v>
       </c>
       <c r="E21" t="n">
-        <v>13.26346548650494</v>
+        <v>13.21279888551785</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594550672549277</v>
+        <v>0.7592148200086377</v>
       </c>
       <c r="G21" t="n">
-        <v>21.51523375026347</v>
+        <v>21.40095565356269</v>
       </c>
       <c r="H21" t="n">
-        <v>38.93245692861156</v>
+        <v>39.10724268932071</v>
       </c>
       <c r="I21" t="n">
-        <v>1.658884689344039</v>
+        <v>1.553150747796698</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746594170343299</v>
+        <v>4.745092625053984</v>
       </c>
       <c r="K21" t="n">
-        <v>17.95990596942735</v>
+        <v>18.07410286238533</v>
       </c>
       <c r="L21" t="n">
-        <v>45.30739797638909</v>
+        <v>45.3768109503437</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94474108895767</v>
+        <v>99.94826100399436</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_37_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_37_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.45149506921209</v>
+        <v>43.7309228901195</v>
       </c>
       <c r="M2" t="n">
-        <v>99.48498799293822</v>
+        <v>94.43826589609452</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.95058982549477</v>
+        <v>81.59574088837901</v>
       </c>
       <c r="C3" t="n">
-        <v>45.87757144713562</v>
+        <v>43.35129644393457</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228572451674404</v>
+        <v>2.185942631772112</v>
       </c>
       <c r="E3" t="n">
-        <v>5.673020101311374</v>
+        <v>4.172341622784556</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428574838914682</v>
+        <v>0.737716741031933</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95617157846053</v>
+        <v>32.88022041957219</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17144425900754</v>
+        <v>33.93497008746891</v>
       </c>
       <c r="I3" t="n">
-        <v>6.535664676827774</v>
+        <v>3.073819754299721</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642859274321676</v>
+        <v>4.610729631449581</v>
       </c>
       <c r="K3" t="n">
-        <v>12.04941017450522</v>
+        <v>18.40425911162099</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83840488228306</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7653865039239</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.03890193383434</v>
+        <v>88.78730683723339</v>
       </c>
       <c r="C4" t="n">
-        <v>42.59666492879234</v>
+        <v>42.95651371801575</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184589399740646</v>
+        <v>2.191743758138517</v>
       </c>
       <c r="E4" t="n">
-        <v>6.470686027470659</v>
+        <v>6.568259773078397</v>
       </c>
       <c r="F4" t="n">
-        <v>0.74441017891356</v>
+        <v>0.7396745179539509</v>
       </c>
       <c r="G4" t="n">
-        <v>33.28601339855263</v>
+        <v>33.57083507611038</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24286823002376</v>
+        <v>34.02502782588174</v>
       </c>
       <c r="I4" t="n">
-        <v>5.45777108092334</v>
+        <v>7.068800148858196</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65256361820975</v>
+        <v>4.622965737212193</v>
       </c>
       <c r="K4" t="n">
-        <v>12.96109806616564</v>
+        <v>11.21269316276663</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26069076401903</v>
+        <v>45.59579010630475</v>
       </c>
       <c r="M4" t="n">
-        <v>99.818453758977</v>
+        <v>99.76499698708712</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.85418334386563</v>
+        <v>87.85052199130409</v>
       </c>
       <c r="C5" t="n">
-        <v>42.25900417594814</v>
+        <v>43.11550607780448</v>
       </c>
       <c r="D5" t="n">
-        <v>2.126636446201062</v>
+        <v>2.148041401691045</v>
       </c>
       <c r="E5" t="n">
-        <v>7.058395854787079</v>
+        <v>7.421268807515153</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457270135129337</v>
+        <v>0.7413314751742899</v>
       </c>
       <c r="G5" t="n">
-        <v>32.402999506682</v>
+        <v>32.90144815745822</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30344262159495</v>
+        <v>34.10124785801733</v>
       </c>
       <c r="I5" t="n">
-        <v>4.556188066631769</v>
+        <v>5.903862571608747</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660793834455835</v>
+        <v>4.633321719839312</v>
       </c>
       <c r="K5" t="n">
-        <v>14.14581665613435</v>
+        <v>12.14947800869591</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44357441566962</v>
+        <v>44.53866035380909</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84839524775212</v>
+        <v>99.80364444030948</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.47266998043949</v>
+        <v>86.74885599742046</v>
       </c>
       <c r="C6" t="n">
-        <v>41.58504935590025</v>
+        <v>42.93040476067853</v>
       </c>
       <c r="D6" t="n">
-        <v>2.059076684684114</v>
+        <v>2.096285462875105</v>
       </c>
       <c r="E6" t="n">
-        <v>7.467915579578186</v>
+        <v>8.063991199585779</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468459719701123</v>
+        <v>0.7427355951577226</v>
       </c>
       <c r="G6" t="n">
-        <v>31.37360921149741</v>
+        <v>32.10870490006445</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35491471062516</v>
+        <v>34.16583737725524</v>
       </c>
       <c r="I6" t="n">
-        <v>3.802520497271322</v>
+        <v>4.929203992746399</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667787324813201</v>
+        <v>4.642097469735766</v>
       </c>
       <c r="K6" t="n">
-        <v>15.52733001956049</v>
+        <v>13.25114400257953</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76105984491059</v>
+        <v>43.65445505419727</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87343922037132</v>
+        <v>99.83600381745535</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.87667465251677</v>
+        <v>85.43828534357496</v>
       </c>
       <c r="C7" t="n">
-        <v>40.57957996665031</v>
+        <v>42.38575816949675</v>
       </c>
       <c r="D7" t="n">
-        <v>1.981253891129603</v>
+        <v>2.034549640493862</v>
       </c>
       <c r="E7" t="n">
-        <v>7.71446754552068</v>
+        <v>8.512216406672858</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477990350506681</v>
+        <v>0.74392780460198</v>
       </c>
       <c r="G7" t="n">
-        <v>30.18784379980229</v>
+        <v>31.16310023996086</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39875561233073</v>
+        <v>34.22067901169108</v>
       </c>
       <c r="I7" t="n">
-        <v>3.172810799616117</v>
+        <v>4.114263461391946</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673743969066675</v>
+        <v>4.649548778762376</v>
       </c>
       <c r="K7" t="n">
-        <v>17.12332534748323</v>
+        <v>14.56171465642506</v>
       </c>
       <c r="L7" t="n">
-        <v>42.1914691164978</v>
+        <v>42.91560484094634</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89437443063134</v>
+        <v>99.86307766686814</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.83220540927729</v>
+        <v>83.96555607477137</v>
       </c>
       <c r="C8" t="n">
-        <v>42.90518810186798</v>
+        <v>41.55249030367486</v>
       </c>
       <c r="D8" t="n">
-        <v>1.985523131373752</v>
+        <v>1.96538702025035</v>
       </c>
       <c r="E8" t="n">
-        <v>9.565677083283553</v>
+        <v>8.795055842544068</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494104053799669</v>
+        <v>0.7449417410597721</v>
       </c>
       <c r="G8" t="n">
-        <v>30.6970303252282</v>
+        <v>30.10373966963644</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47287864747848</v>
+        <v>34.26732008874951</v>
       </c>
       <c r="I8" t="n">
-        <v>5.677870782908548</v>
+        <v>3.433225830907646</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683815033624793</v>
+        <v>4.655885881623576</v>
       </c>
       <c r="K8" t="n">
-        <v>12.16779459072271</v>
+        <v>16.03444392522864</v>
       </c>
       <c r="L8" t="n">
-        <v>44.73816189689279</v>
+        <v>42.29878067494674</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81114458948348</v>
+        <v>99.88571490385024</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.83711336746617</v>
+        <v>82.33061589513069</v>
       </c>
       <c r="C9" t="n">
-        <v>41.79114206774723</v>
+        <v>40.45102101480936</v>
       </c>
       <c r="D9" t="n">
-        <v>1.895242944519623</v>
+        <v>1.888941654668955</v>
       </c>
       <c r="E9" t="n">
-        <v>9.920778020036678</v>
+        <v>8.930354722000764</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507899200807023</v>
+        <v>0.7458056424464234</v>
       </c>
       <c r="G9" t="n">
-        <v>29.30126031890699</v>
+        <v>28.9328296347674</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53633632371231</v>
+        <v>34.30705955253548</v>
       </c>
       <c r="I9" t="n">
-        <v>4.740268839705494</v>
+        <v>2.864339423421529</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692437000504389</v>
+        <v>4.661285265290147</v>
       </c>
       <c r="K9" t="n">
-        <v>14.16288663253381</v>
+        <v>17.66938410486931</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8882526668604</v>
+        <v>41.78422749612946</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84228136714144</v>
+        <v>99.90463261580813</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.62661828824652</v>
+        <v>86.69814327552729</v>
       </c>
       <c r="C10" t="n">
-        <v>40.31594679650564</v>
+        <v>43.51552250739496</v>
       </c>
       <c r="D10" t="n">
-        <v>1.796181473448327</v>
+        <v>1.891012196863075</v>
       </c>
       <c r="E10" t="n">
-        <v>10.06164295941691</v>
+        <v>10.68817589775235</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519739392314666</v>
+        <v>0.7466231489307986</v>
       </c>
       <c r="G10" t="n">
-        <v>27.76972793155406</v>
+        <v>30.23741031544625</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59080120464747</v>
+        <v>35.61753113502071</v>
       </c>
       <c r="I10" t="n">
-        <v>3.95645365975163</v>
+        <v>2.850995900696617</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699837120196666</v>
+        <v>4.666394680817492</v>
       </c>
       <c r="K10" t="n">
-        <v>16.37338171175347</v>
+        <v>13.30185672447271</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17899735730462</v>
+        <v>43.08769162695511</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86832586556372</v>
+        <v>99.90507085882278</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.31804790714712</v>
+        <v>86.57424671525132</v>
       </c>
       <c r="C11" t="n">
-        <v>38.62046337529465</v>
+        <v>43.71524881502345</v>
       </c>
       <c r="D11" t="n">
-        <v>1.693831086225341</v>
+        <v>1.875641117734204</v>
       </c>
       <c r="E11" t="n">
-        <v>10.03855944059215</v>
+        <v>11.0738188825041</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529916087686005</v>
+        <v>0.7473213538473584</v>
       </c>
       <c r="G11" t="n">
-        <v>26.18734750458364</v>
+        <v>30.05934779219325</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63761400335563</v>
+        <v>35.71856093298057</v>
       </c>
       <c r="I11" t="n">
-        <v>3.301506708818015</v>
+        <v>2.428798174445852</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706197554803753</v>
+        <v>4.670758461545991</v>
       </c>
       <c r="K11" t="n">
-        <v>18.68195209285287</v>
+        <v>13.42575328474866</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58768304130383</v>
+        <v>42.77811360006321</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89009850945135</v>
+        <v>99.91911569983533</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.88218316932488</v>
+        <v>84.87918076405288</v>
       </c>
       <c r="C12" t="n">
-        <v>36.69540750079442</v>
+        <v>42.3983962748646</v>
       </c>
       <c r="D12" t="n">
-        <v>1.586868705322758</v>
+        <v>1.803151470511521</v>
       </c>
       <c r="E12" t="n">
-        <v>9.863718821985378</v>
+        <v>10.98344012582511</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538680566651994</v>
+        <v>0.7479158382683233</v>
       </c>
       <c r="G12" t="n">
-        <v>24.5336636978614</v>
+        <v>28.89761621326931</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67793060659918</v>
+        <v>35.74697458382116</v>
       </c>
       <c r="I12" t="n">
-        <v>2.754457926733474</v>
+        <v>2.025608543180423</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711675354157496</v>
+        <v>4.674473989177021</v>
       </c>
       <c r="K12" t="n">
-        <v>21.11781683067512</v>
+        <v>15.12081923594712</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09506714884106</v>
+        <v>42.41331787323143</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90829148031061</v>
+        <v>99.93253338404315</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.40497386083445</v>
+        <v>86.01588752593801</v>
       </c>
       <c r="C13" t="n">
-        <v>34.64347357427948</v>
+        <v>43.36426581130574</v>
       </c>
       <c r="D13" t="n">
-        <v>1.47910749971269</v>
+        <v>1.804449979678545</v>
       </c>
       <c r="E13" t="n">
-        <v>9.576839711760776</v>
+        <v>11.61261361253892</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546237445805013</v>
+        <v>0.7484544372646008</v>
       </c>
       <c r="G13" t="n">
-        <v>22.86762972211684</v>
+        <v>29.22997582760801</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71269225070306</v>
+        <v>36.08426664824952</v>
       </c>
       <c r="I13" t="n">
-        <v>2.297682528332427</v>
+        <v>1.858286787694647</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716398403628133</v>
+        <v>4.677840232903756</v>
       </c>
       <c r="K13" t="n">
-        <v>23.59502613916558</v>
+        <v>13.98411247406199</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68498756636789</v>
+        <v>42.5897233967404</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92348727981295</v>
+        <v>99.93810168210813</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.30200307718037</v>
+        <v>84.21415468667315</v>
       </c>
       <c r="C14" t="n">
-        <v>39.01749067001647</v>
+        <v>41.85185640500501</v>
       </c>
       <c r="D14" t="n">
-        <v>1.480782677600891</v>
+        <v>1.729276352961905</v>
       </c>
       <c r="E14" t="n">
-        <v>11.99564958279398</v>
+        <v>11.38708426509579</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554784011967905</v>
+        <v>0.7489134838852236</v>
       </c>
       <c r="G14" t="n">
-        <v>24.82976965497598</v>
+        <v>28.01225113778732</v>
       </c>
       <c r="H14" t="n">
-        <v>36.68824742676535</v>
+        <v>36.10639806980014</v>
       </c>
       <c r="I14" t="n">
-        <v>2.830335326367454</v>
+        <v>1.54952210286012</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72174000747994</v>
+        <v>4.680709274282648</v>
       </c>
       <c r="K14" t="n">
-        <v>16.69799692281962</v>
+        <v>15.78584531332687</v>
       </c>
       <c r="L14" t="n">
-        <v>44.19027462621972</v>
+        <v>42.31067920423215</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90576221905582</v>
+        <v>99.94838092256401</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.5170565177269</v>
+        <v>83.43082801093165</v>
       </c>
       <c r="C15" t="n">
-        <v>38.66983588577629</v>
+        <v>41.29121709137329</v>
       </c>
       <c r="D15" t="n">
-        <v>1.451822676283683</v>
+        <v>1.696339702829054</v>
       </c>
       <c r="E15" t="n">
-        <v>12.15452497909294</v>
+        <v>11.38846011751267</v>
       </c>
       <c r="F15" t="n">
-        <v>0.75619889076876</v>
+        <v>0.7493053240881618</v>
       </c>
       <c r="G15" t="n">
-        <v>24.34416824108108</v>
+        <v>27.47871598964365</v>
       </c>
       <c r="H15" t="n">
-        <v>36.72323651400193</v>
+        <v>36.12528935517751</v>
       </c>
       <c r="I15" t="n">
-        <v>2.36086214919376</v>
+        <v>1.3095592461296</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72624306730475</v>
+        <v>4.683158275551012</v>
       </c>
       <c r="K15" t="n">
-        <v>17.48294348227311</v>
+        <v>16.56917198906836</v>
       </c>
       <c r="L15" t="n">
-        <v>43.76860020621817</v>
+        <v>42.09598177196238</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92137957426756</v>
+        <v>99.95637085240402</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.03255742006652</v>
+        <v>81.17138475699282</v>
       </c>
       <c r="C16" t="n">
-        <v>36.55011321028746</v>
+        <v>39.23526110876384</v>
       </c>
       <c r="D16" t="n">
-        <v>1.35788914981084</v>
+        <v>1.602569448985622</v>
       </c>
       <c r="E16" t="n">
-        <v>11.69628861919508</v>
+        <v>10.94089367682228</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568190361035405</v>
+        <v>0.7496412729584377</v>
       </c>
       <c r="G16" t="n">
-        <v>22.76909050652852</v>
+        <v>25.95974772559653</v>
       </c>
       <c r="H16" t="n">
-        <v>36.75335259071165</v>
+        <v>36.14148602395473</v>
       </c>
       <c r="I16" t="n">
-        <v>1.968998542069765</v>
+        <v>1.091788652684991</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730118975647128</v>
+        <v>4.685257955990236</v>
       </c>
       <c r="K16" t="n">
-        <v>19.96744257993348</v>
+        <v>18.82861524300717</v>
       </c>
       <c r="L16" t="n">
-        <v>43.41686470563481</v>
+        <v>41.89974700250319</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93442049585573</v>
+        <v>99.9636233542742</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.84386229944781</v>
+        <v>85.48653898128518</v>
       </c>
       <c r="C17" t="n">
-        <v>37.87498873240698</v>
+        <v>42.09183042785523</v>
       </c>
       <c r="D17" t="n">
-        <v>1.358959953059777</v>
+        <v>1.603325238286741</v>
       </c>
       <c r="E17" t="n">
-        <v>12.5148242818011</v>
+        <v>12.46700309022837</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574158479145999</v>
+        <v>0.7499948119917309</v>
       </c>
       <c r="G17" t="n">
-        <v>23.27365608100005</v>
+        <v>27.29135825550583</v>
       </c>
       <c r="H17" t="n">
-        <v>37.2689458645177</v>
+        <v>37.47789837314092</v>
       </c>
       <c r="I17" t="n">
-        <v>1.936211221688321</v>
+        <v>1.209491637183259</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733849049466249</v>
+        <v>4.687467574948319</v>
       </c>
       <c r="K17" t="n">
-        <v>18.1561377005522</v>
+        <v>14.51346101871483</v>
       </c>
       <c r="L17" t="n">
-        <v>43.90438404808303</v>
+        <v>43.35441117021104</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9355104810422</v>
+        <v>99.9597026167811</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.46828810957362</v>
+        <v>87.02915914896816</v>
       </c>
       <c r="C18" t="n">
-        <v>35.79820019913585</v>
+        <v>42.80788574406056</v>
       </c>
       <c r="D18" t="n">
-        <v>1.272916134766849</v>
+        <v>1.604547966081895</v>
       </c>
       <c r="E18" t="n">
-        <v>11.99153684795485</v>
+        <v>13.05161782031765</v>
       </c>
       <c r="F18" t="n">
-        <v>0.75792880943708</v>
+        <v>0.7505667729893781</v>
       </c>
       <c r="G18" t="n">
-        <v>21.80006281554965</v>
+        <v>27.4337993318794</v>
       </c>
       <c r="H18" t="n">
-        <v>37.2941863387757</v>
+        <v>37.50647976570589</v>
       </c>
       <c r="I18" t="n">
-        <v>1.614602104107729</v>
+        <v>1.991105160810337</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737055058981749</v>
+        <v>4.691042331183614</v>
       </c>
       <c r="K18" t="n">
-        <v>20.53171189042637</v>
+        <v>12.97084085103182</v>
       </c>
       <c r="L18" t="n">
-        <v>43.61630426539089</v>
+        <v>44.15495380952639</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94621635495312</v>
+        <v>99.93368040461877</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.56865378331003</v>
+        <v>84.49296121720218</v>
       </c>
       <c r="C19" t="n">
-        <v>35.147060573682</v>
+        <v>40.58087634294822</v>
       </c>
       <c r="D19" t="n">
-        <v>1.240965896555288</v>
+        <v>1.508851053939553</v>
       </c>
       <c r="E19" t="n">
-        <v>11.91492724201635</v>
+        <v>12.54992926239303</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583617119429414</v>
+        <v>0.7510584103516237</v>
       </c>
       <c r="G19" t="n">
-        <v>21.25288049853757</v>
+        <v>25.79761896214933</v>
       </c>
       <c r="H19" t="n">
-        <v>37.31548747750944</v>
+        <v>37.53104731577967</v>
       </c>
       <c r="I19" t="n">
-        <v>1.346270257105044</v>
+        <v>1.660341147891325</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739760699643383</v>
+        <v>4.694115064697649</v>
       </c>
       <c r="K19" t="n">
-        <v>21.43134621668998</v>
+        <v>15.50703878279781</v>
       </c>
       <c r="L19" t="n">
-        <v>43.37674315118056</v>
+        <v>43.85677639756479</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95514994155255</v>
+        <v>99.94469152331081</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.93971996340088</v>
+        <v>81.90686104962933</v>
       </c>
       <c r="C20" t="n">
-        <v>32.72518350929648</v>
+        <v>38.25196045846781</v>
       </c>
       <c r="D20" t="n">
-        <v>1.146717067806402</v>
+        <v>1.411743515894212</v>
       </c>
       <c r="E20" t="n">
-        <v>11.19708692437004</v>
+        <v>11.97296627279789</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587353499764223</v>
+        <v>0.7514815589194558</v>
       </c>
       <c r="G20" t="n">
-        <v>19.63876757239885</v>
+        <v>24.13732038045349</v>
       </c>
       <c r="H20" t="n">
-        <v>37.33387248447895</v>
+        <v>37.55219242074357</v>
       </c>
       <c r="I20" t="n">
-        <v>1.122444627017573</v>
+        <v>1.3843971575741</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742095937352638</v>
+        <v>4.6967597432466</v>
       </c>
       <c r="K20" t="n">
-        <v>24.06028003659913</v>
+        <v>18.09313895037068</v>
       </c>
       <c r="L20" t="n">
-        <v>43.1771400580737</v>
+        <v>43.60878000372009</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96260360396931</v>
+        <v>99.95387941255856</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.92589713761465</v>
+        <v>79.22895765423233</v>
       </c>
       <c r="C21" t="n">
-        <v>36.49734719126532</v>
+        <v>35.78788571566447</v>
       </c>
       <c r="D21" t="n">
-        <v>1.147441716354094</v>
+        <v>1.311625658481644</v>
       </c>
       <c r="E21" t="n">
-        <v>13.21279888551785</v>
+        <v>11.31623964032351</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592148200086377</v>
+        <v>0.7518464837615662</v>
       </c>
       <c r="G21" t="n">
-        <v>21.40095565356269</v>
+        <v>22.4255527874279</v>
       </c>
       <c r="H21" t="n">
-        <v>39.10724268932071</v>
+        <v>37.57042803508086</v>
       </c>
       <c r="I21" t="n">
-        <v>1.553150747796698</v>
+        <v>1.154224525647068</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745092625053984</v>
+        <v>4.699040523509789</v>
       </c>
       <c r="K21" t="n">
-        <v>18.07410286238533</v>
+        <v>20.77104234576766</v>
       </c>
       <c r="L21" t="n">
-        <v>45.3768109503437</v>
+        <v>43.40261646196859</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94826100399436</v>
+        <v>99.96154452340072</v>
       </c>
     </row>
   </sheetData>
